--- a/tams-invest-parent/tams-invest-product/src/main/resources/tpl/FinProductBmQuotation.xlsx
+++ b/tams-invest-parent/tams-invest-product/src/main/resources/tpl/FinProductBmQuotation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>产品代码</t>
   </si>
@@ -51,10 +51,6 @@
   </si>
   <si>
     <t>发送状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>发送备注</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -404,55 +400,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="17.875" customWidth="1"/>
-    <col min="3" max="4" width="16.375" customWidth="1"/>
-    <col min="5" max="5" width="17.5" customWidth="1"/>
-    <col min="6" max="6" width="17.25" customWidth="1"/>
-    <col min="7" max="7" width="19.25" customWidth="1"/>
-    <col min="8" max="8" width="18.25" customWidth="1"/>
-    <col min="9" max="9" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="17.90625" customWidth="1"/>
+    <col min="4" max="5" width="16.36328125" customWidth="1"/>
+    <col min="6" max="6" width="17.453125" customWidth="1"/>
+    <col min="7" max="7" width="17.26953125" customWidth="1"/>
+    <col min="8" max="8" width="19.26953125" customWidth="1"/>
+    <col min="9" max="9" width="18.26953125" customWidth="1"/>
+    <col min="10" max="10" width="15.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>9</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>6</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
